--- a/web/sample-data/전표테스트_샘플.xlsx
+++ b/web/sample-data/전표테스트_샘플.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:J43"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -1595,9 +1595,201 @@
         <v>결산 조정</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>JE-0019</v>
+      </c>
+      <c r="B38" t="str">
+        <v>2024-02-10</v>
+      </c>
+      <c r="C38" t="str">
+        <v>13:00</v>
+      </c>
+      <c r="D38" t="str">
+        <v>매출채권</v>
+      </c>
+      <c r="E38" t="str">
+        <v>순환에너지㈜</v>
+      </c>
+      <c r="F38">
+        <v>5000000</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38" t="str">
+        <v>김민지</v>
+      </c>
+      <c r="I38" t="str">
+        <v>박준호</v>
+      </c>
+      <c r="J38" t="str">
+        <v>제품 매출</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>JE-0019</v>
+      </c>
+      <c r="B39" t="str">
+        <v>2024-02-10</v>
+      </c>
+      <c r="C39" t="str">
+        <v>13:00</v>
+      </c>
+      <c r="D39" t="str">
+        <v>매출액</v>
+      </c>
+      <c r="E39" t="str">
+        <v>순환에너지㈜</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>5000000</v>
+      </c>
+      <c r="H39" t="str">
+        <v>김민지</v>
+      </c>
+      <c r="I39" t="str">
+        <v>박준호</v>
+      </c>
+      <c r="J39" t="str">
+        <v>제품 매출</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>JE-0020</v>
+      </c>
+      <c r="B40" t="str">
+        <v>2024-02-13</v>
+      </c>
+      <c r="C40" t="str">
+        <v>16:30</v>
+      </c>
+      <c r="D40" t="str">
+        <v>재고자산</v>
+      </c>
+      <c r="E40" t="str">
+        <v>순환에너지㈜</v>
+      </c>
+      <c r="F40">
+        <v>5000000</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40" t="str">
+        <v>이서연</v>
+      </c>
+      <c r="I40" t="str">
+        <v>박준호</v>
+      </c>
+      <c r="J40" t="str">
+        <v>원재료 매입</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>JE-0020</v>
+      </c>
+      <c r="B41" t="str">
+        <v>2024-02-13</v>
+      </c>
+      <c r="C41" t="str">
+        <v>16:30</v>
+      </c>
+      <c r="D41" t="str">
+        <v>매입채무</v>
+      </c>
+      <c r="E41" t="str">
+        <v>순환에너지㈜</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>5000000</v>
+      </c>
+      <c r="H41" t="str">
+        <v>이서연</v>
+      </c>
+      <c r="I41" t="str">
+        <v>박준호</v>
+      </c>
+      <c r="J41" t="str">
+        <v>원재료 매입</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>JE-0021</v>
+      </c>
+      <c r="B42" t="str">
+        <v>2024-01-12</v>
+      </c>
+      <c r="C42" t="str">
+        <v>10:20</v>
+      </c>
+      <c r="D42" t="str">
+        <v>현금및현금성자산</v>
+      </c>
+      <c r="E42" t="str">
+        <v>(주)대한상사</v>
+      </c>
+      <c r="F42">
+        <v>3452000</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42" t="str">
+        <v>김민지</v>
+      </c>
+      <c r="I42" t="str">
+        <v>박준호</v>
+      </c>
+      <c r="J42" t="str">
+        <v>매출채권 회수</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>JE-0021</v>
+      </c>
+      <c r="B43" t="str">
+        <v>2024-01-12</v>
+      </c>
+      <c r="C43" t="str">
+        <v>10:20</v>
+      </c>
+      <c r="D43" t="str">
+        <v>매출채권</v>
+      </c>
+      <c r="E43" t="str">
+        <v>(주)대한상사</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>3452000</v>
+      </c>
+      <c r="H43" t="str">
+        <v>김민지</v>
+      </c>
+      <c r="I43" t="str">
+        <v>박준호</v>
+      </c>
+      <c r="J43" t="str">
+        <v>매출채권 회수</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J43"/>
   </ignoredErrors>
 </worksheet>
 </file>